--- a/Template_insertion_cotisation.xlsx
+++ b/Template_insertion_cotisation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\sebtp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32ACDBED-030D-48E2-8D52-B913A75C471F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9377094-7401-40C1-A6FC-89817B4EC741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F4D428C-24DD-4466-884B-80274E11BF8D}"/>
+    <workbookView xWindow="5760" yWindow="1992" windowWidth="17280" windowHeight="8880" xr2:uid="{4F4D428C-24DD-4466-884B-80274E11BF8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>nom_adherent</t>
-  </si>
-  <si>
-    <t>periode</t>
-  </si>
-  <si>
     <t>montant_paye</t>
   </si>
   <si>
@@ -48,10 +42,16 @@
     <t>observation</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
     <t>montant_attendu</t>
+  </si>
+  <si>
+    <t>nom_adherent (obligatoire)</t>
+  </si>
+  <si>
+    <t>periode (obligatoire)</t>
+  </si>
+  <si>
+    <t>OTI</t>
   </si>
 </sst>
 </file>
@@ -422,8 +422,8 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" customWidth="1"/>
@@ -434,36 +434,36 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C2" s="1">
         <v>800000</v>
